--- a/data/processed/2024-03/MIR_2024-03_horario.xlsx
+++ b/data/processed/2024-03/MIR_2024-03_horario.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8678" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8680" uniqueCount="273">
   <si>
     <t>FECHA_HORA</t>
   </si>
@@ -769,6 +769,9 @@
     <t>Fuente</t>
   </si>
   <si>
+    <t>Proceso</t>
+  </si>
+  <si>
     <t>Norma</t>
   </si>
   <si>
@@ -797,6 +800,9 @@
   </si>
   <si>
     <t>SEMADET Jalisco, BD_2024.xlsx (hoja Data), estación Miravalle (MIR). Unidades de la hoja Param.</t>
+  </si>
+  <si>
+    <t>etl.py (limpieza del año) → calculos.py (Archivo1 horario y Archivo2 diario) → procesar.py (JSON del sitio y Excel).</t>
   </si>
   <si>
     <t>NOM-172-SEMARNAT-2023. Criterios validados en Actividades 5 y 6 (SFE, enero 2025).</t>
@@ -76835,7 +76841,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="61" width="14.7109375" customWidth="1"/>
@@ -76854,7 +76860,7 @@
         <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -76862,7 +76868,7 @@
         <v>250</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -76870,31 +76876,31 @@
         <v>251</v>
       </c>
       <c r="B4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>252</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -76902,7 +76908,7 @@
         <v>253</v>
       </c>
       <c r="B8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -76910,7 +76916,7 @@
         <v>254</v>
       </c>
       <c r="B9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -76918,7 +76924,7 @@
         <v>255</v>
       </c>
       <c r="B10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -76926,7 +76932,7 @@
         <v>256</v>
       </c>
       <c r="B11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -76934,7 +76940,7 @@
         <v>257</v>
       </c>
       <c r="B12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -76942,7 +76948,15 @@
         <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>270</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/2024-03/MIR_2024-03_horario.xlsx
+++ b/data/processed/2024-03/MIR_2024-03_horario.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8680" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8684" uniqueCount="277">
   <si>
     <t>FECHA_HORA</t>
   </si>
@@ -178,19 +178,19 @@
     <t>Muy alto</t>
   </si>
   <si>
-    <t>La calidad del aire es buena. Se pueden realizar actividades al aire libre con normalidad.</t>
+    <t>Disfruta las actividades al aire libre.</t>
   </si>
   <si>
-    <t>Calidad del aire aceptable. Las actividades al aire libre pueden continuar.</t>
+    <t>Disfruta las actividades al aire libre. Infórmate sobre la evolución de la calidad del aire.</t>
   </si>
   <si>
-    <t>Calidad del aire mala. Reduzcan la actividad física intensa al aire libre.</t>
+    <t>Es posible realizar actividades al aire libre. Si presenta síntomas como tos o falta de aire, toma más descansos y realiza actividades menos vigorosas. Infórmate sobre la evolución de la calidad del aire.</t>
   </si>
   <si>
-    <t>Calidad del aire muy mala. Eviten la actividad física al aire libre.</t>
+    <t>Reduce las actividades físicas al aire libre y de preferencia realízalas en espacios interiores, siempre y cuando se trate de un espacio libre de humo de tabaco. Evita la actividad física vigorosa o prolongada al aire libre. Infórmate sobre la evolución de la calidad del aire.</t>
   </si>
   <si>
-    <t>Sin información suficiente para estimar la calidad del aire en esta hora.</t>
+    <t>Sin información suficiente para calcular el Índice AIRE Y SALUD en esta hora.</t>
   </si>
   <si>
     <t>NE</t>
@@ -784,6 +784,12 @@
     <t>Bandas</t>
   </si>
   <si>
+    <t>Redondeo</t>
+  </si>
+  <si>
+    <t>Mensajes</t>
+  </si>
+  <si>
     <t>Suficiencia diaria</t>
   </si>
   <si>
@@ -820,7 +826,13 @@
     <t>NowCast 12 h con la función de referencia de la profesora (≥ 2 de las 3 horas recientes; W ≥ 0.5; factor 0.714 PM10 / 0.694 PM2.5). Diario = promedio 24 h redondeado a entero.</t>
   </si>
   <si>
-    <t>O3: 0.058/0.090/0.135/0.175 ppm · CO: 5/9/12/16 ppm · PM10: 45/60/132/213 µg/m³ · PM2.5: 15/33/79/130 µg/m³.</t>
+    <t>Tablas 4 a 9 de la NOM. O3: 0.058/0.090/0.135/0.175 ppm · CO: 5/9/12/16 ppm · PM10: 45/60/132/213 µg/m³ · PM2.5: 15/33/79/130 µg/m³. Para partículas se usa la columna «a partir de enero de 2024», que corresponde al año de los datos.</t>
+  </si>
+  <si>
+    <t>Numeral 5.2.4: O3 a 3 decimales, CO a 2 y PM a entero; si la cifra siguiente es 5 o más, se sube. En marzo 2024 el redondeo interno de la función NowCast de referencia coincide con esta regla en todas las horas.</t>
+  </si>
+  <si>
+    <t>Tabla 12 de la NOM, textos oficiales para tres grupos: población en general; menores de 12 años y personas gestantes; personas con enfermedades cardiovasculares o respiratorias y mayores de 60 años.</t>
   </si>
   <si>
     <t>≥ 18 de 24 datos horarios válidos (75 %) por contaminante; si no cumple, no se calcula indicador.</t>
@@ -76841,7 +76853,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="61" width="14.7109375" customWidth="1"/>
@@ -76860,7 +76872,7 @@
         <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -76868,7 +76880,7 @@
         <v>250</v>
       </c>
       <c r="B3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -76876,7 +76888,7 @@
         <v>251</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -76884,7 +76896,7 @@
         <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -76892,7 +76904,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -76900,7 +76912,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -76908,7 +76920,7 @@
         <v>253</v>
       </c>
       <c r="B8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -76916,7 +76928,7 @@
         <v>254</v>
       </c>
       <c r="B9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -76924,7 +76936,7 @@
         <v>255</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -76932,7 +76944,7 @@
         <v>256</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -76940,7 +76952,7 @@
         <v>257</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -76948,7 +76960,7 @@
         <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -76956,7 +76968,23 @@
         <v>259</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/2024-03/MIR_2024-03_horario.xlsx
+++ b/data/processed/2024-03/MIR_2024-03_horario.xlsx
@@ -826,7 +826,7 @@
     <t>NowCast 12 h con la función de referencia de la profesora (≥ 2 de las 3 horas recientes; W ≥ 0.5; factor 0.714 PM10 / 0.694 PM2.5). Diario = promedio 24 h redondeado a entero.</t>
   </si>
   <si>
-    <t>Tablas 4 a 9 de la NOM. O3: 0.058/0.090/0.135/0.175 ppm · CO: 5/9/12/16 ppm · PM10: 45/60/132/213 µg/m³ · PM2.5: 15/33/79/130 µg/m³. Para partículas se usa la columna «a partir de enero de 2024», que corresponde al año de los datos.</t>
+    <t>Tablas 4 a 9 de la NOM. O3: 0.058/0.090/0.135/0.175 ppm · CO: 5/9/12/16 ppm · PM10: 45/60/132/213 µg/m³ · PM2.5: 15/33/79/130 µg/m³. Para partículas se usa la columna «a partir de enero de 2024», que corresponde a la fecha de los datos.</t>
   </si>
   <si>
     <t>Numeral 5.2.4: O3 a 3 decimales, CO a 2 y PM a entero; si la cifra siguiente es 5 o más, se sube. En marzo 2024 el redondeo interno de la función NowCast de referencia coincide con esta regla en todas las horas.</t>
